--- a/data/macro/USA/Nonfarm Payrolls.xlsx
+++ b/data/macro/USA/Nonfarm Payrolls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0D73AE-B48F-417B-8932-6427E29DA80D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22841549-867B-9A45-BB8C-13113A46C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAYEMS" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -59,28 +70,28 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -88,14 +99,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -104,7 +115,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -136,26 +147,26 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -434,17 +445,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G674"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="4" customWidth="1"/>
-    <col min="5" max="7" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -467,7 +478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>25538</v>
       </c>
@@ -506,7 +517,7 @@
         <v>-33000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>25569</v>
       </c>
@@ -545,7 +556,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>25600</v>
       </c>
@@ -569,7 +580,7 @@
         <v>-64000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>25628</v>
       </c>
@@ -593,7 +604,7 @@
         <v>128000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>25659</v>
       </c>
@@ -617,7 +628,7 @@
         <v>148000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>25689</v>
       </c>
@@ -641,7 +652,7 @@
         <v>-104000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>25720</v>
       </c>
@@ -665,7 +676,7 @@
         <v>-225000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>25750</v>
       </c>
@@ -689,7 +700,7 @@
         <v>-94000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>25781</v>
       </c>
@@ -713,7 +724,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>25812</v>
       </c>
@@ -737,7 +748,7 @@
         <v>-120000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>25842</v>
       </c>
@@ -761,7 +772,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>25873</v>
       </c>
@@ -785,7 +796,7 @@
         <v>-429000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>25903</v>
       </c>
@@ -809,7 +820,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>25934</v>
       </c>
@@ -833,7 +844,7 @@
         <v>381000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>25965</v>
       </c>
@@ -857,7 +868,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>25993</v>
       </c>
@@ -881,7 +892,7 @@
         <v>-60000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>26024</v>
       </c>
@@ -905,7 +916,7 @@
         <v>53000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>26054</v>
       </c>
@@ -929,7 +940,7 @@
         <v>178000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>26085</v>
       </c>
@@ -953,7 +964,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>26115</v>
       </c>
@@ -977,7 +988,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>26146</v>
       </c>
@@ -1001,7 +1012,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>26177</v>
       </c>
@@ -1025,7 +1036,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>26207</v>
       </c>
@@ -1049,7 +1060,7 @@
         <v>247000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>26238</v>
       </c>
@@ -1073,7 +1084,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26268</v>
       </c>
@@ -1097,7 +1108,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26299</v>
       </c>
@@ -1121,7 +1132,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26330</v>
       </c>
@@ -1145,7 +1156,7 @@
         <v>337000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26359</v>
       </c>
@@ -1169,7 +1180,7 @@
         <v>207000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>26390</v>
       </c>
@@ -1193,7 +1204,7 @@
         <v>293000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>26420</v>
       </c>
@@ -1217,7 +1228,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>26451</v>
       </c>
@@ -1241,7 +1252,7 @@
         <v>304000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>26481</v>
       </c>
@@ -1265,7 +1276,7 @@
         <v>293000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>26512</v>
       </c>
@@ -1289,7 +1300,7 @@
         <v>-52000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>26543</v>
       </c>
@@ -1313,7 +1324,7 @@
         <v>430000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>26573</v>
       </c>
@@ -1337,7 +1348,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>26604</v>
       </c>
@@ -1361,7 +1372,7 @@
         <v>410000</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>26634</v>
       </c>
@@ -1385,7 +1396,7 @@
         <v>294000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>26665</v>
       </c>
@@ -1409,7 +1420,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>26696</v>
       </c>
@@ -1433,7 +1444,7 @@
         <v>351000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>26724</v>
       </c>
@@ -1457,7 +1468,7 @@
         <v>396000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>26755</v>
       </c>
@@ -1481,7 +1492,7 @@
         <v>268000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>26785</v>
       </c>
@@ -1505,7 +1516,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>26816</v>
       </c>
@@ -1529,7 +1540,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>26846</v>
       </c>
@@ -1553,7 +1564,7 @@
         <v>241000</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>26877</v>
       </c>
@@ -1577,7 +1588,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>26908</v>
       </c>
@@ -1601,7 +1612,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>26938</v>
       </c>
@@ -1625,7 +1636,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>26969</v>
       </c>
@@ -1649,7 +1660,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>26999</v>
       </c>
@@ -1673,7 +1684,7 @@
         <v>306000</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>27030</v>
       </c>
@@ -1697,7 +1708,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>27061</v>
       </c>
@@ -1721,7 +1732,7 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>27089</v>
       </c>
@@ -1745,7 +1756,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>27120</v>
       </c>
@@ -1769,7 +1780,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>27150</v>
       </c>
@@ -1793,7 +1804,7 @@
         <v>86000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>27181</v>
       </c>
@@ -1817,7 +1828,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>27211</v>
       </c>
@@ -1841,7 +1852,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>27242</v>
       </c>
@@ -1865,7 +1876,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>27273</v>
       </c>
@@ -1889,7 +1900,7 @@
         <v>-16000</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>27303</v>
       </c>
@@ -1913,7 +1924,7 @@
         <v>-8000</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>27334</v>
       </c>
@@ -1937,7 +1948,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>27364</v>
       </c>
@@ -1961,7 +1972,7 @@
         <v>-368000</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>27395</v>
       </c>
@@ -1985,7 +1996,7 @@
         <v>-604000</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>27426</v>
       </c>
@@ -2009,7 +2020,7 @@
         <v>-360000</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>27454</v>
       </c>
@@ -2033,7 +2044,7 @@
         <v>-378000</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>27485</v>
       </c>
@@ -2057,7 +2068,7 @@
         <v>-270000</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>27515</v>
       </c>
@@ -2096,7 +2107,7 @@
         <v>-188000</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>27546</v>
       </c>
@@ -2120,7 +2131,7 @@
         <v>162000</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>27576</v>
       </c>
@@ -2144,7 +2155,7 @@
         <v>-103000</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>27607</v>
       </c>
@@ -2168,7 +2179,7 @@
         <v>249000</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>27638</v>
       </c>
@@ -2192,7 +2203,7 @@
         <v>386000</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>27668</v>
       </c>
@@ -2216,7 +2227,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>27699</v>
       </c>
@@ -2240,7 +2251,7 @@
         <v>305000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>27729</v>
       </c>
@@ -2264,7 +2275,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>27760</v>
       </c>
@@ -2288,7 +2299,7 @@
         <v>338000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>27791</v>
       </c>
@@ -2312,7 +2323,7 @@
         <v>488000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>27820</v>
       </c>
@@ -2336,7 +2347,7 @@
         <v>311000</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>27851</v>
       </c>
@@ -2360,7 +2371,7 @@
         <v>232000</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>27881</v>
       </c>
@@ -2384,7 +2395,7 @@
         <v>243000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>27912</v>
       </c>
@@ -2408,7 +2419,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>27942</v>
       </c>
@@ -2432,7 +2443,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>27973</v>
       </c>
@@ -2456,7 +2467,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>28004</v>
       </c>
@@ -2480,7 +2491,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>28034</v>
       </c>
@@ -2504,7 +2515,7 @@
         <v>188000</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>28065</v>
       </c>
@@ -2528,7 +2539,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>28095</v>
       </c>
@@ -2552,7 +2563,7 @@
         <v>332000</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>28126</v>
       </c>
@@ -2576,7 +2587,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>28157</v>
       </c>
@@ -2600,7 +2611,7 @@
         <v>244000</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>28185</v>
       </c>
@@ -2624,7 +2635,7 @@
         <v>296000</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>28216</v>
       </c>
@@ -2648,7 +2659,7 @@
         <v>403000</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>28246</v>
       </c>
@@ -2672,7 +2683,7 @@
         <v>338000</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>28277</v>
       </c>
@@ -2696,7 +2707,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>28307</v>
       </c>
@@ -2720,7 +2731,7 @@
         <v>399000</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>28338</v>
       </c>
@@ -2744,7 +2755,7 @@
         <v>348000</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>28369</v>
       </c>
@@ -2768,7 +2779,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>28399</v>
       </c>
@@ -2792,7 +2803,7 @@
         <v>458000</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>28430</v>
       </c>
@@ -2816,7 +2827,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>28460</v>
       </c>
@@ -2840,7 +2851,7 @@
         <v>379000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>28491</v>
       </c>
@@ -2864,7 +2875,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>28522</v>
       </c>
@@ -2888,7 +2899,7 @@
         <v>187000</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>28550</v>
       </c>
@@ -2912,7 +2923,7 @@
         <v>353000</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>28581</v>
       </c>
@@ -2936,7 +2947,7 @@
         <v>513000</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>28611</v>
       </c>
@@ -2960,7 +2971,7 @@
         <v>702000</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>28642</v>
       </c>
@@ -2984,7 +2995,7 @@
         <v>346000</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>28672</v>
       </c>
@@ -3008,7 +3019,7 @@
         <v>442000</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>28703</v>
       </c>
@@ -3032,7 +3043,7 @@
         <v>254000</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>28734</v>
       </c>
@@ -3056,7 +3067,7 @@
         <v>276000</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>28764</v>
       </c>
@@ -3080,7 +3091,7 @@
         <v>137000</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>28795</v>
       </c>
@@ -3104,7 +3115,7 @@
         <v>336000</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>28825</v>
       </c>
@@ -3128,7 +3139,7 @@
         <v>437000</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>28856</v>
       </c>
@@ -3152,7 +3163,7 @@
         <v>282000</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>28887</v>
       </c>
@@ -3176,7 +3187,7 @@
         <v>137000</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>28915</v>
       </c>
@@ -3200,7 +3211,7 @@
         <v>244000</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>28946</v>
       </c>
@@ -3224,7 +3235,7 @@
         <v>426000</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>28976</v>
       </c>
@@ -3248,7 +3259,7 @@
         <v>-62000</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>29007</v>
       </c>
@@ -3272,7 +3283,7 @@
         <v>373000</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>29037</v>
       </c>
@@ -3296,7 +3307,7 @@
         <v>318000</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>29068</v>
       </c>
@@ -3320,7 +3331,7 @@
         <v>106000</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>29099</v>
       </c>
@@ -3344,7 +3355,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>29129</v>
       </c>
@@ -3368,7 +3379,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>29160</v>
       </c>
@@ -3392,7 +3403,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>29190</v>
       </c>
@@ -3416,7 +3427,7 @@
         <v>94000</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>29221</v>
       </c>
@@ -3440,7 +3451,7 @@
         <v>97000</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>29252</v>
       </c>
@@ -3464,7 +3475,7 @@
         <v>129000</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>29281</v>
       </c>
@@ -3488,7 +3499,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>29312</v>
       </c>
@@ -3512,7 +3523,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>29342</v>
       </c>
@@ -3536,7 +3547,7 @@
         <v>-144000</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>29373</v>
       </c>
@@ -3560,7 +3571,7 @@
         <v>-431000</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>29403</v>
       </c>
@@ -3584,7 +3595,7 @@
         <v>-320000</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>29434</v>
       </c>
@@ -3608,7 +3619,7 @@
         <v>-262000</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>29465</v>
       </c>
@@ -3647,7 +3658,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>29495</v>
       </c>
@@ -3671,7 +3682,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>29526</v>
       </c>
@@ -3695,7 +3706,7 @@
         <v>281000</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>29556</v>
       </c>
@@ -3719,7 +3730,7 @@
         <v>257000</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>29587</v>
       </c>
@@ -3743,7 +3754,7 @@
         <v>195000</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>29618</v>
       </c>
@@ -3767,7 +3778,7 @@
         <v>94000</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>29646</v>
       </c>
@@ -3791,7 +3802,7 @@
         <v>68000</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>29677</v>
       </c>
@@ -3815,7 +3826,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>29707</v>
       </c>
@@ -3839,7 +3850,7 @@
         <v>73000</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>29738</v>
       </c>
@@ -3863,7 +3874,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>29768</v>
       </c>
@@ -3887,7 +3898,7 @@
         <v>197000</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>29799</v>
       </c>
@@ -3911,7 +3922,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>29830</v>
       </c>
@@ -3935,7 +3946,7 @@
         <v>-36000</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>29860</v>
       </c>
@@ -3959,7 +3970,7 @@
         <v>-87000</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>29891</v>
       </c>
@@ -3983,7 +3994,7 @@
         <v>-99000</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>29921</v>
       </c>
@@ -4007,7 +4018,7 @@
         <v>-209000</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>29952</v>
       </c>
@@ -4031,7 +4042,7 @@
         <v>-278000</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>29983</v>
       </c>
@@ -4055,7 +4066,7 @@
         <v>-326000</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>30011</v>
       </c>
@@ -4079,7 +4090,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>30042</v>
       </c>
@@ -4103,7 +4114,7 @@
         <v>-130000</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>30072</v>
       </c>
@@ -4127,7 +4138,7 @@
         <v>-280000</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>30103</v>
       </c>
@@ -4151,7 +4162,7 @@
         <v>-45000</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>30133</v>
       </c>
@@ -4175,7 +4186,7 @@
         <v>-243000</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>30164</v>
       </c>
@@ -4199,7 +4210,7 @@
         <v>-342000</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>30195</v>
       </c>
@@ -4223,7 +4234,7 @@
         <v>-158000</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>30225</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>-181000</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>30256</v>
       </c>
@@ -4271,7 +4282,7 @@
         <v>-277000</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>30286</v>
       </c>
@@ -4295,7 +4306,7 @@
         <v>-123000</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>30317</v>
       </c>
@@ -4319,7 +4330,7 @@
         <v>-14000</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>30348</v>
       </c>
@@ -4343,7 +4354,7 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>30376</v>
       </c>
@@ -4367,7 +4378,7 @@
         <v>-75000</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>30407</v>
       </c>
@@ -4391,7 +4402,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>30437</v>
       </c>
@@ -4415,7 +4426,7 @@
         <v>276000</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>30468</v>
       </c>
@@ -4439,7 +4450,7 @@
         <v>277000</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>30498</v>
       </c>
@@ -4463,7 +4474,7 @@
         <v>379000</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>30529</v>
       </c>
@@ -4487,7 +4498,7 @@
         <v>418000</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>30560</v>
       </c>
@@ -4511,7 +4522,7 @@
         <v>-308000</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>30590</v>
       </c>
@@ -4535,7 +4546,7 @@
         <v>1115000</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>30621</v>
       </c>
@@ -4559,7 +4570,7 @@
         <v>271000</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>30651</v>
       </c>
@@ -4583,7 +4594,7 @@
         <v>353000</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>30682</v>
       </c>
@@ -4607,7 +4618,7 @@
         <v>356000</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>30713</v>
       </c>
@@ -4631,7 +4642,7 @@
         <v>446000</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>30742</v>
       </c>
@@ -4655,7 +4666,7 @@
         <v>481000</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>30773</v>
       </c>
@@ -4679,7 +4690,7 @@
         <v>275000</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>30803</v>
       </c>
@@ -4703,7 +4714,7 @@
         <v>363000</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>30834</v>
       </c>
@@ -4727,7 +4738,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>30864</v>
       </c>
@@ -4751,7 +4762,7 @@
         <v>379000</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>30895</v>
       </c>
@@ -4775,7 +4786,7 @@
         <v>313000</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>30926</v>
       </c>
@@ -4799,7 +4810,7 @@
         <v>242000</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>30956</v>
       </c>
@@ -4823,7 +4834,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>30987</v>
       </c>
@@ -4847,7 +4858,7 @@
         <v>286000</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>31017</v>
       </c>
@@ -4871,7 +4882,7 @@
         <v>349000</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>31048</v>
       </c>
@@ -4895,7 +4906,7 @@
         <v>128000</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>31079</v>
       </c>
@@ -4919,7 +4930,7 @@
         <v>266000</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>31107</v>
       </c>
@@ -4943,7 +4954,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>31138</v>
       </c>
@@ -4967,7 +4978,7 @@
         <v>346000</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>31168</v>
       </c>
@@ -4991,7 +5002,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>31199</v>
       </c>
@@ -5015,7 +5026,7 @@
         <v>274000</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>31229</v>
       </c>
@@ -5039,7 +5050,7 @@
         <v>146000</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>31260</v>
       </c>
@@ -5063,7 +5074,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>31291</v>
       </c>
@@ -5087,7 +5098,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>31321</v>
       </c>
@@ -5111,7 +5122,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>31352</v>
       </c>
@@ -5135,7 +5146,7 @@
         <v>188000</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>31382</v>
       </c>
@@ -5159,7 +5170,7 @@
         <v>209000</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>31413</v>
       </c>
@@ -5198,7 +5209,7 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>31444</v>
       </c>
@@ -5222,7 +5233,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>31472</v>
       </c>
@@ -5246,7 +5257,7 @@
         <v>107000</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>31503</v>
       </c>
@@ -5270,7 +5281,7 @@
         <v>94000</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>31533</v>
       </c>
@@ -5294,7 +5305,7 @@
         <v>187000</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>31564</v>
       </c>
@@ -5318,7 +5329,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>31594</v>
       </c>
@@ -5342,7 +5353,7 @@
         <v>-94000</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>31625</v>
       </c>
@@ -5366,7 +5377,7 @@
         <v>318000</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>31656</v>
       </c>
@@ -5390,7 +5401,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>31686</v>
       </c>
@@ -5414,7 +5425,7 @@
         <v>347000</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>31717</v>
       </c>
@@ -5438,7 +5449,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>31747</v>
       </c>
@@ -5462,7 +5473,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>31778</v>
       </c>
@@ -5486,7 +5497,7 @@
         <v>205000</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>31809</v>
       </c>
@@ -5510,7 +5521,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>31837</v>
       </c>
@@ -5534,7 +5545,7 @@
         <v>232000</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>31868</v>
       </c>
@@ -5558,7 +5569,7 @@
         <v>249000</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>31898</v>
       </c>
@@ -5582,7 +5593,7 @@
         <v>338000</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>31929</v>
       </c>
@@ -5606,7 +5617,7 @@
         <v>226000</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>31959</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>31990</v>
       </c>
@@ -5654,7 +5665,7 @@
         <v>347000</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>32021</v>
       </c>
@@ -5678,7 +5689,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>32051</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>32082</v>
       </c>
@@ -5726,7 +5737,7 @@
         <v>492000</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>32112</v>
       </c>
@@ -5750,7 +5761,7 @@
         <v>232000</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>32143</v>
       </c>
@@ -5774,7 +5785,7 @@
         <v>294000</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>32174</v>
       </c>
@@ -5798,7 +5809,7 @@
         <v>94000</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>32203</v>
       </c>
@@ -5822,7 +5833,7 @@
         <v>453000</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>32234</v>
       </c>
@@ -5846,7 +5857,7 @@
         <v>276000</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>32264</v>
       </c>
@@ -5870,7 +5881,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>32295</v>
       </c>
@@ -5894,7 +5905,7 @@
         <v>229000</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>32325</v>
       </c>
@@ -5918,7 +5929,7 @@
         <v>363000</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>32356</v>
       </c>
@@ -5942,7 +5953,7 @@
         <v>222000</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>32387</v>
       </c>
@@ -5966,7 +5977,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>32417</v>
       </c>
@@ -5990,7 +6001,7 @@
         <v>339000</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>32448</v>
       </c>
@@ -6014,7 +6025,7 @@
         <v>268000</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>32478</v>
       </c>
@@ -6038,7 +6049,7 @@
         <v>339000</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>32509</v>
       </c>
@@ -6062,7 +6073,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>32540</v>
       </c>
@@ -6086,7 +6097,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>32568</v>
       </c>
@@ -6110,7 +6121,7 @@
         <v>258000</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>32599</v>
       </c>
@@ -6134,7 +6145,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>32629</v>
       </c>
@@ -6158,7 +6169,7 @@
         <v>173000</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>32660</v>
       </c>
@@ -6182,7 +6193,7 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>32690</v>
       </c>
@@ -6206,7 +6217,7 @@
         <v>116000</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>32721</v>
       </c>
@@ -6230,7 +6241,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>32752</v>
       </c>
@@ -6254,7 +6265,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>32782</v>
       </c>
@@ -6278,7 +6289,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>32813</v>
       </c>
@@ -6302,7 +6313,7 @@
         <v>111000</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>32843</v>
       </c>
@@ -6326,7 +6337,7 @@
         <v>277000</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>32874</v>
       </c>
@@ -6350,7 +6361,7 @@
         <v>96000</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>32905</v>
       </c>
@@ -6374,7 +6385,7 @@
         <v>335000</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>32933</v>
       </c>
@@ -6398,7 +6409,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>32964</v>
       </c>
@@ -6422,7 +6433,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>32994</v>
       </c>
@@ -6446,7 +6457,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>33025</v>
       </c>
@@ -6470,7 +6481,7 @@
         <v>152000</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>33055</v>
       </c>
@@ -6494,7 +6505,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>33086</v>
       </c>
@@ -6518,7 +6529,7 @@
         <v>-28000</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>33117</v>
       </c>
@@ -6542,7 +6553,7 @@
         <v>-221000</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>33147</v>
       </c>
@@ -6566,7 +6577,7 @@
         <v>-88000</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>33178</v>
       </c>
@@ -6590,7 +6601,7 @@
         <v>-159000</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>33208</v>
       </c>
@@ -6614,7 +6625,7 @@
         <v>-150000</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>33239</v>
       </c>
@@ -6638,7 +6649,7 @@
         <v>-56000</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>33270</v>
       </c>
@@ -6662,7 +6673,7 @@
         <v>-120000</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>33298</v>
       </c>
@@ -6686,7 +6697,7 @@
         <v>-305000</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>33329</v>
       </c>
@@ -6710,7 +6721,7 @@
         <v>-158000</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>33359</v>
       </c>
@@ -6749,7 +6760,7 @@
         <v>-211000</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>33390</v>
       </c>
@@ -6773,7 +6784,7 @@
         <v>-125000</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>33420</v>
       </c>
@@ -6797,7 +6808,7 @@
         <v>97000</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>33451</v>
       </c>
@@ -6821,7 +6832,7 @@
         <v>-36000</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>33482</v>
       </c>
@@ -6845,7 +6856,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>33512</v>
       </c>
@@ -6869,7 +6880,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>33543</v>
       </c>
@@ -6893,7 +6904,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>33573</v>
       </c>
@@ -6917,7 +6928,7 @@
         <v>-57000</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>33604</v>
       </c>
@@ -6941,7 +6952,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>33635</v>
       </c>
@@ -6965,7 +6976,7 @@
         <v>53000</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>33664</v>
       </c>
@@ -6989,7 +7000,7 @@
         <v>-63000</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>33695</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v>54000</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>33725</v>
       </c>
@@ -7037,7 +7048,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>33756</v>
       </c>
@@ -7061,7 +7072,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>33786</v>
       </c>
@@ -7085,7 +7096,7 @@
         <v>67000</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>33817</v>
       </c>
@@ -7109,7 +7120,7 @@
         <v>68000</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>33848</v>
       </c>
@@ -7133,7 +7144,7 @@
         <v>141000</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>33878</v>
       </c>
@@ -7157,7 +7168,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>33909</v>
       </c>
@@ -7181,7 +7192,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>33939</v>
       </c>
@@ -7205,7 +7216,7 @@
         <v>138000</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>33970</v>
       </c>
@@ -7229,7 +7240,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>34001</v>
       </c>
@@ -7253,7 +7264,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>34029</v>
       </c>
@@ -7277,7 +7288,7 @@
         <v>242000</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>34060</v>
       </c>
@@ -7301,7 +7312,7 @@
         <v>-49000</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>34090</v>
       </c>
@@ -7325,7 +7336,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>34121</v>
       </c>
@@ -7349,7 +7360,7 @@
         <v>267000</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>34151</v>
       </c>
@@ -7373,7 +7384,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>34182</v>
       </c>
@@ -7397,7 +7408,7 @@
         <v>298000</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>34213</v>
       </c>
@@ -7421,7 +7432,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>34243</v>
       </c>
@@ -7445,7 +7456,7 @@
         <v>239000</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>34274</v>
       </c>
@@ -7469,7 +7480,7 @@
         <v>286000</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>34304</v>
       </c>
@@ -7493,7 +7504,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>34335</v>
       </c>
@@ -7517,7 +7528,7 @@
         <v>312000</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>34366</v>
       </c>
@@ -7541,7 +7552,7 @@
         <v>272000</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>34394</v>
       </c>
@@ -7565,7 +7576,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>34425</v>
       </c>
@@ -7589,7 +7600,7 @@
         <v>465000</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>34455</v>
       </c>
@@ -7613,7 +7624,7 @@
         <v>349000</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>34486</v>
       </c>
@@ -7637,7 +7648,7 @@
         <v>334000</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>34516</v>
       </c>
@@ -7661,7 +7672,7 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>34547</v>
       </c>
@@ -7685,7 +7696,7 @@
         <v>378000</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>34578</v>
       </c>
@@ -7709,7 +7720,7 @@
         <v>277000</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>34608</v>
       </c>
@@ -7733,7 +7744,7 @@
         <v>352000</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>34639</v>
       </c>
@@ -7757,7 +7768,7 @@
         <v>213000</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>34669</v>
       </c>
@@ -7781,7 +7792,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>34700</v>
       </c>
@@ -7805,7 +7816,7 @@
         <v>275000</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>34731</v>
       </c>
@@ -7829,7 +7840,7 @@
         <v>326000</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>34759</v>
       </c>
@@ -7853,7 +7864,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>34790</v>
       </c>
@@ -7877,7 +7888,7 @@
         <v>222000</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>34820</v>
       </c>
@@ -7901,7 +7912,7 @@
         <v>162000</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>34851</v>
       </c>
@@ -7925,7 +7936,7 @@
         <v>-16000</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>34881</v>
       </c>
@@ -7949,7 +7960,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>34912</v>
       </c>
@@ -7973,7 +7984,7 @@
         <v>102000</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>34943</v>
       </c>
@@ -7997,7 +8008,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>34973</v>
       </c>
@@ -8021,7 +8032,7 @@
         <v>242000</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>35004</v>
       </c>
@@ -8045,7 +8056,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
         <v>35034</v>
       </c>
@@ -8069,7 +8080,7 @@
         <v>149000</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
         <v>35065</v>
       </c>
@@ -8093,7 +8104,7 @@
         <v>133000</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
         <v>35096</v>
       </c>
@@ -8117,7 +8128,7 @@
         <v>-19000</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
         <v>35125</v>
       </c>
@@ -8141,7 +8152,7 @@
         <v>431000</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
         <v>35156</v>
       </c>
@@ -8165,7 +8176,7 @@
         <v>267000</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
         <v>35186</v>
       </c>
@@ -8189,7 +8200,7 @@
         <v>164000</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
         <v>35217</v>
       </c>
@@ -8213,7 +8224,7 @@
         <v>321000</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
         <v>35247</v>
       </c>
@@ -8237,7 +8248,7 @@
         <v>288000</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
         <v>35278</v>
       </c>
@@ -8261,7 +8272,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
         <v>35309</v>
       </c>
@@ -8300,7 +8311,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" s="2">
         <v>35339</v>
       </c>
@@ -8324,7 +8335,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
         <v>35370</v>
       </c>
@@ -8348,7 +8359,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>35400</v>
       </c>
@@ -8372,7 +8383,7 @@
         <v>298000</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>35431</v>
       </c>
@@ -8396,7 +8407,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>35462</v>
       </c>
@@ -8420,7 +8431,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>35490</v>
       </c>
@@ -8444,7 +8455,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>35521</v>
       </c>
@@ -8468,7 +8479,7 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>35551</v>
       </c>
@@ -8492,7 +8503,7 @@
         <v>292000</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>35582</v>
       </c>
@@ -8516,7 +8527,7 @@
         <v>259000</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>35612</v>
       </c>
@@ -8540,7 +8551,7 @@
         <v>267000</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>35643</v>
       </c>
@@ -8564,7 +8575,7 @@
         <v>313000</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>35674</v>
       </c>
@@ -8588,7 +8599,7 @@
         <v>-39000</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>35704</v>
       </c>
@@ -8612,7 +8623,7 @@
         <v>512000</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>35735</v>
       </c>
@@ -8636,7 +8647,7 @@
         <v>341000</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
         <v>35765</v>
       </c>
@@ -8660,7 +8671,7 @@
         <v>306000</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
         <v>35796</v>
       </c>
@@ -8684,7 +8695,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
         <v>35827</v>
       </c>
@@ -8708,7 +8719,7 @@
         <v>276000</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
         <v>35855</v>
       </c>
@@ -8732,7 +8743,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
         <v>35886</v>
       </c>
@@ -8756,7 +8767,7 @@
         <v>151000</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
         <v>35916</v>
       </c>
@@ -8780,7 +8791,7 @@
         <v>279000</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
         <v>35947</v>
       </c>
@@ -8804,7 +8815,7 @@
         <v>406000</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
         <v>35977</v>
       </c>
@@ -8828,7 +8839,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
         <v>36008</v>
       </c>
@@ -8852,7 +8863,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
         <v>36039</v>
       </c>
@@ -8876,7 +8887,7 @@
         <v>347000</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
         <v>36069</v>
       </c>
@@ -8900,7 +8911,7 @@
         <v>223000</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
         <v>36100</v>
       </c>
@@ -8924,7 +8935,7 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>36130</v>
       </c>
@@ -8948,7 +8959,7 @@
         <v>282000</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>36161</v>
       </c>
@@ -8972,7 +8983,7 @@
         <v>347000</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>36192</v>
       </c>
@@ -8996,7 +9007,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>36220</v>
       </c>
@@ -9020,7 +9031,7 @@
         <v>411000</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>36251</v>
       </c>
@@ -9044,7 +9055,7 @@
         <v>107000</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>36281</v>
       </c>
@@ -9068,7 +9079,7 @@
         <v>376000</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>36312</v>
       </c>
@@ -9092,7 +9103,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>36342</v>
       </c>
@@ -9116,7 +9127,7 @@
         <v>261000</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>36373</v>
       </c>
@@ -9140,7 +9151,7 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>36404</v>
       </c>
@@ -9164,7 +9175,7 @@
         <v>166000</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>36434</v>
       </c>
@@ -9188,7 +9199,7 @@
         <v>214000</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>36465</v>
       </c>
@@ -9212,7 +9223,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
         <v>36495</v>
       </c>
@@ -9236,7 +9247,7 @@
         <v>292000</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
         <v>36526</v>
       </c>
@@ -9260,7 +9271,7 @@
         <v>295000</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
         <v>36557</v>
       </c>
@@ -9284,7 +9295,7 @@
         <v>231000</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
         <v>36586</v>
       </c>
@@ -9308,7 +9319,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
         <v>36617</v>
       </c>
@@ -9332,7 +9343,7 @@
         <v>467000</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
         <v>36647</v>
       </c>
@@ -9356,7 +9367,7 @@
         <v>287000</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
         <v>36678</v>
       </c>
@@ -9380,7 +9391,7 @@
         <v>226000</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
         <v>36708</v>
       </c>
@@ -9404,7 +9415,7 @@
         <v>-47000</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
         <v>36739</v>
       </c>
@@ -9428,7 +9439,7 @@
         <v>179000</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
         <v>36770</v>
       </c>
@@ -9452,7 +9463,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
         <v>36800</v>
       </c>
@@ -9476,7 +9487,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
         <v>36831</v>
       </c>
@@ -9500,7 +9511,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>36861</v>
       </c>
@@ -9524,7 +9535,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>36892</v>
       </c>
@@ -9548,7 +9559,7 @@
         <v>142000</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>36923</v>
       </c>
@@ -9572,7 +9583,7 @@
         <v>-27000</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>36951</v>
       </c>
@@ -9596,7 +9607,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>36982</v>
       </c>
@@ -9620,7 +9631,7 @@
         <v>-25000</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>37012</v>
       </c>
@@ -9644,7 +9655,7 @@
         <v>-282000</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>37043</v>
       </c>
@@ -9668,7 +9679,7 @@
         <v>-38000</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>37073</v>
       </c>
@@ -9692,7 +9703,7 @@
         <v>-131000</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>37104</v>
       </c>
@@ -9716,7 +9727,7 @@
         <v>-112000</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>37135</v>
       </c>
@@ -9740,7 +9751,7 @@
         <v>-160000</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>37165</v>
       </c>
@@ -9764,7 +9775,7 @@
         <v>-241000</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>37196</v>
       </c>
@@ -9788,7 +9799,7 @@
         <v>-325000</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
         <v>37226</v>
       </c>
@@ -9812,7 +9823,7 @@
         <v>-294000</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
         <v>37257</v>
       </c>
@@ -9851,7 +9862,7 @@
         <v>-171000</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
         <v>37288</v>
       </c>
@@ -9875,7 +9886,7 @@
         <v>-139000</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
         <v>37316</v>
       </c>
@@ -9899,7 +9910,7 @@
         <v>-134000</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
         <v>37347</v>
       </c>
@@ -9923,7 +9934,7 @@
         <v>-20000</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
         <v>37377</v>
       </c>
@@ -9947,7 +9958,7 @@
         <v>-80000</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
         <v>37408</v>
       </c>
@@ -9971,7 +9982,7 @@
         <v>-8000</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
         <v>37438</v>
       </c>
@@ -9995,7 +10006,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
         <v>37469</v>
       </c>
@@ -10019,7 +10030,7 @@
         <v>-84000</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
         <v>37500</v>
       </c>
@@ -10043,7 +10054,7 @@
         <v>-16000</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
         <v>37530</v>
       </c>
@@ -10067,7 +10078,7 @@
         <v>-60000</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
         <v>37561</v>
       </c>
@@ -10091,7 +10102,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>37591</v>
       </c>
@@ -10115,7 +10126,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>37622</v>
       </c>
@@ -10139,7 +10150,7 @@
         <v>-157000</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>37653</v>
       </c>
@@ -10163,7 +10174,7 @@
         <v>91000</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>37681</v>
       </c>
@@ -10187,7 +10198,7 @@
         <v>-151000</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>37712</v>
       </c>
@@ -10211,7 +10222,7 @@
         <v>-210000</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>37742</v>
       </c>
@@ -10235,7 +10246,7 @@
         <v>-44000</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>37773</v>
       </c>
@@ -10259,7 +10270,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>37803</v>
       </c>
@@ -10283,7 +10294,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>37834</v>
       </c>
@@ -10307,7 +10318,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>37865</v>
       </c>
@@ -10331,7 +10342,7 @@
         <v>-43000</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>37895</v>
       </c>
@@ -10355,7 +10366,7 @@
         <v>103000</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>37926</v>
       </c>
@@ -10379,7 +10390,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
         <v>37956</v>
       </c>
@@ -10403,7 +10414,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
         <v>37987</v>
       </c>
@@ -10427,7 +10438,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
         <v>38018</v>
       </c>
@@ -10451,7 +10462,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
         <v>38047</v>
       </c>
@@ -10475,7 +10486,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
         <v>38078</v>
       </c>
@@ -10499,7 +10510,7 @@
         <v>331000</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
         <v>38108</v>
       </c>
@@ -10523,7 +10534,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
         <v>38139</v>
       </c>
@@ -10547,7 +10558,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
         <v>38169</v>
       </c>
@@ -10571,7 +10582,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
         <v>38200</v>
       </c>
@@ -10595,7 +10606,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
         <v>38231</v>
       </c>
@@ -10619,7 +10630,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
         <v>38261</v>
       </c>
@@ -10643,7 +10654,7 @@
         <v>162000</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
         <v>38292</v>
       </c>
@@ -10667,7 +10678,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>38322</v>
       </c>
@@ -10691,7 +10702,7 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>38353</v>
       </c>
@@ -10715,7 +10726,7 @@
         <v>129000</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>38384</v>
       </c>
@@ -10739,7 +10750,7 @@
         <v>134000</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>38412</v>
       </c>
@@ -10763,7 +10774,7 @@
         <v>239000</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>38443</v>
       </c>
@@ -10787,7 +10798,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
         <v>38473</v>
       </c>
@@ -10811,7 +10822,7 @@
         <v>363000</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
         <v>38504</v>
       </c>
@@ -10835,7 +10846,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
         <v>38534</v>
       </c>
@@ -10859,7 +10870,7 @@
         <v>243000</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
         <v>38565</v>
       </c>
@@ -10883,7 +10894,7 @@
         <v>375000</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
         <v>38596</v>
       </c>
@@ -10907,7 +10918,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
         <v>38626</v>
       </c>
@@ -10931,7 +10942,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
         <v>38657</v>
       </c>
@@ -10955,7 +10966,7 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" s="2">
         <v>38687</v>
       </c>
@@ -10979,7 +10990,7 @@
         <v>337000</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" s="2">
         <v>38718</v>
       </c>
@@ -11003,7 +11014,7 @@
         <v>158000</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" s="2">
         <v>38749</v>
       </c>
@@ -11027,7 +11038,7 @@
         <v>277000</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" s="2">
         <v>38777</v>
       </c>
@@ -11051,7 +11062,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" s="2">
         <v>38808</v>
       </c>
@@ -11075,7 +11086,7 @@
         <v>281000</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" s="2">
         <v>38838</v>
       </c>
@@ -11099,7 +11110,7 @@
         <v>182000</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" s="2">
         <v>38869</v>
       </c>
@@ -11123,7 +11134,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" s="2">
         <v>38899</v>
       </c>
@@ -11147,7 +11158,7 @@
         <v>77000</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" s="2">
         <v>38930</v>
       </c>
@@ -11171,7 +11182,7 @@
         <v>206000</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" s="2">
         <v>38961</v>
       </c>
@@ -11195,7 +11206,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" s="2">
         <v>38991</v>
       </c>
@@ -11219,7 +11230,7 @@
         <v>156000</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" s="2">
         <v>39022</v>
       </c>
@@ -11243,7 +11254,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
         <v>39052</v>
       </c>
@@ -11267,7 +11278,7 @@
         <v>209000</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
         <v>39083</v>
       </c>
@@ -11291,7 +11302,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
         <v>39114</v>
       </c>
@@ -11315,7 +11326,7 @@
         <v>111000</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
         <v>39142</v>
       </c>
@@ -11339,7 +11350,7 @@
         <v>97000</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
         <v>39173</v>
       </c>
@@ -11363,7 +11374,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
         <v>39203</v>
       </c>
@@ -11402,7 +11413,7 @@
         <v>88000</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
         <v>39234</v>
       </c>
@@ -11426,7 +11437,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
         <v>39264</v>
       </c>
@@ -11450,7 +11461,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
         <v>39295</v>
       </c>
@@ -11474,7 +11485,7 @@
         <v>92000</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
         <v>39326</v>
       </c>
@@ -11498,7 +11509,7 @@
         <v>-4000</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
         <v>39356</v>
       </c>
@@ -11522,7 +11533,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
         <v>39387</v>
       </c>
@@ -11546,7 +11557,7 @@
         <v>166000</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
         <v>39417</v>
       </c>
@@ -11570,7 +11581,7 @@
         <v>94000</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" s="2">
         <v>39448</v>
       </c>
@@ -11594,7 +11605,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" s="2">
         <v>39479</v>
       </c>
@@ -11618,7 +11629,7 @@
         <v>-17000</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" s="2">
         <v>39508</v>
       </c>
@@ -11642,7 +11653,7 @@
         <v>-63000</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" s="2">
         <v>39539</v>
       </c>
@@ -11666,7 +11677,7 @@
         <v>-80000</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" s="2">
         <v>39569</v>
       </c>
@@ -11690,7 +11701,7 @@
         <v>-20000</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A464" s="2">
         <v>39600</v>
       </c>
@@ -11714,7 +11725,7 @@
         <v>-49000</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A465" s="2">
         <v>39630</v>
       </c>
@@ -11738,7 +11749,7 @@
         <v>-62000</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A466" s="2">
         <v>39661</v>
       </c>
@@ -11762,7 +11773,7 @@
         <v>-51000</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A467" s="2">
         <v>39692</v>
       </c>
@@ -11786,7 +11797,7 @@
         <v>-84000</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A468" s="2">
         <v>39722</v>
       </c>
@@ -11810,7 +11821,7 @@
         <v>-159000</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A469" s="2">
         <v>39753</v>
       </c>
@@ -11834,7 +11845,7 @@
         <v>-240000</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A470" s="2">
         <v>39783</v>
       </c>
@@ -11858,7 +11869,7 @@
         <v>-533000</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A471" s="2">
         <v>39814</v>
       </c>
@@ -11882,7 +11893,7 @@
         <v>-524000</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A472" s="2">
         <v>39845</v>
       </c>
@@ -11906,7 +11917,7 @@
         <v>-598000</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A473" s="2">
         <v>39873</v>
       </c>
@@ -11930,7 +11941,7 @@
         <v>-651000</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A474" s="2">
         <v>39904</v>
       </c>
@@ -11954,7 +11965,7 @@
         <v>-699000</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A475" s="2">
         <v>39934</v>
       </c>
@@ -11978,7 +11989,7 @@
         <v>-504000</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A476" s="2">
         <v>39965</v>
       </c>
@@ -12002,7 +12013,7 @@
         <v>-322000</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A477" s="2">
         <v>39995</v>
       </c>
@@ -12026,7 +12037,7 @@
         <v>-443000</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A478" s="2">
         <v>40026</v>
       </c>
@@ -12050,7 +12061,7 @@
         <v>-276000</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A479" s="2">
         <v>40057</v>
       </c>
@@ -12074,7 +12085,7 @@
         <v>-201000</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A480" s="2">
         <v>40087</v>
       </c>
@@ -12098,7 +12109,7 @@
         <v>-219000</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481" s="2">
         <v>40118</v>
       </c>
@@ -12122,7 +12133,7 @@
         <v>-111000</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482" s="2">
         <v>40148</v>
       </c>
@@ -12146,7 +12157,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483" s="2">
         <v>40179</v>
       </c>
@@ -12170,7 +12181,7 @@
         <v>-150000</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484" s="2">
         <v>40210</v>
       </c>
@@ -12194,7 +12205,7 @@
         <v>-26000</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485" s="2">
         <v>40238</v>
       </c>
@@ -12218,7 +12229,7 @@
         <v>-14000</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486" s="2">
         <v>40269</v>
       </c>
@@ -12242,7 +12253,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487" s="2">
         <v>40299</v>
       </c>
@@ -12266,7 +12277,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" s="2">
         <v>40330</v>
       </c>
@@ -12290,7 +12301,7 @@
         <v>433000</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" s="2">
         <v>40360</v>
       </c>
@@ -12314,7 +12325,7 @@
         <v>-221000</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" s="2">
         <v>40391</v>
       </c>
@@ -12338,7 +12349,7 @@
         <v>-54000</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" s="2">
         <v>40422</v>
       </c>
@@ -12362,7 +12373,7 @@
         <v>-57000</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" s="2">
         <v>40452</v>
       </c>
@@ -12386,7 +12397,7 @@
         <v>-41000</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" s="2">
         <v>40483</v>
       </c>
@@ -12410,7 +12421,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" s="2">
         <v>40513</v>
       </c>
@@ -12434,7 +12445,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" s="2">
         <v>40544</v>
       </c>
@@ -12458,7 +12469,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" s="2">
         <v>40575</v>
       </c>
@@ -12482,7 +12493,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497" s="2">
         <v>40603</v>
       </c>
@@ -12506,7 +12517,7 @@
         <v>194000</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498" s="2">
         <v>40634</v>
       </c>
@@ -12530,7 +12541,7 @@
         <v>221000</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499" s="2">
         <v>40664</v>
       </c>
@@ -12554,7 +12565,7 @@
         <v>232000</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500" s="2">
         <v>40695</v>
       </c>
@@ -12578,7 +12589,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501" s="2">
         <v>40725</v>
       </c>
@@ -12602,7 +12613,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A502" s="2">
         <v>40756</v>
       </c>
@@ -12626,7 +12637,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A503" s="2">
         <v>40787</v>
       </c>
@@ -12650,7 +12661,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A504" s="2">
         <v>40817</v>
       </c>
@@ -12674,7 +12685,7 @@
         <v>158000</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A505" s="2">
         <v>40848</v>
       </c>
@@ -12698,7 +12709,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A506" s="2">
         <v>40878</v>
       </c>
@@ -12722,7 +12733,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A507" s="2">
         <v>40909</v>
       </c>
@@ -12746,7 +12757,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A508" s="2">
         <v>40940</v>
       </c>
@@ -12770,7 +12781,7 @@
         <v>284000</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A509" s="2">
         <v>40969</v>
       </c>
@@ -12794,7 +12805,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A510" s="2">
         <v>41000</v>
       </c>
@@ -12818,7 +12829,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A511" s="2">
         <v>41030</v>
       </c>
@@ -12842,7 +12853,7 @@
         <v>77000</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A512" s="2">
         <v>41061</v>
       </c>
@@ -12866,7 +12877,7 @@
         <v>77000</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A513" s="2">
         <v>41091</v>
       </c>
@@ -12890,7 +12901,7 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A514" s="2">
         <v>41122</v>
       </c>
@@ -12914,7 +12925,7 @@
         <v>141000</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A515" s="2">
         <v>41153</v>
       </c>
@@ -12953,7 +12964,7 @@
         <v>142000</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A516" s="2">
         <v>41183</v>
       </c>
@@ -12977,7 +12988,7 @@
         <v>148000</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A517" s="2">
         <v>41214</v>
       </c>
@@ -13001,7 +13012,7 @@
         <v>138000</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A518" s="2">
         <v>41244</v>
       </c>
@@ -13025,7 +13036,7 @@
         <v>161000</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A519" s="2">
         <v>41275</v>
       </c>
@@ -13049,7 +13060,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A520" s="2">
         <v>41306</v>
       </c>
@@ -13073,7 +13084,7 @@
         <v>119000</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A521" s="2">
         <v>41334</v>
       </c>
@@ -13097,7 +13108,7 @@
         <v>268000</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A522" s="2">
         <v>41365</v>
       </c>
@@ -13121,7 +13132,7 @@
         <v>138000</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A523" s="2">
         <v>41395</v>
       </c>
@@ -13145,7 +13156,7 @@
         <v>149000</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A524" s="2">
         <v>41426</v>
       </c>
@@ -13169,7 +13180,7 @@
         <v>195000</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A525" s="2">
         <v>41456</v>
       </c>
@@ -13193,7 +13204,7 @@
         <v>188000</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A526" s="2">
         <v>41487</v>
       </c>
@@ -13217,7 +13228,7 @@
         <v>104000</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A527" s="2">
         <v>41518</v>
       </c>
@@ -13241,7 +13252,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A528" s="2">
         <v>41548</v>
       </c>
@@ -13265,7 +13276,7 @@
         <v>163000</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A529" s="2">
         <v>41579</v>
       </c>
@@ -13289,7 +13300,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A530" s="2">
         <v>41609</v>
       </c>
@@ -13313,7 +13324,7 @@
         <v>241000</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A531" s="2">
         <v>41640</v>
       </c>
@@ -13337,7 +13348,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A532" s="2">
         <v>41671</v>
       </c>
@@ -13361,7 +13372,7 @@
         <v>129000</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A533" s="2">
         <v>41699</v>
       </c>
@@ -13385,7 +13396,7 @@
         <v>197000</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A534" s="2">
         <v>41730</v>
       </c>
@@ -13409,7 +13420,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535" s="2">
         <v>41760</v>
       </c>
@@ -13433,7 +13444,7 @@
         <v>282000</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536" s="2">
         <v>41791</v>
       </c>
@@ -13457,7 +13468,7 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537" s="2">
         <v>41821</v>
       </c>
@@ -13481,7 +13492,7 @@
         <v>298000</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538" s="2">
         <v>41852</v>
       </c>
@@ -13505,7 +13516,7 @@
         <v>212000</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539" s="2">
         <v>41883</v>
       </c>
@@ -13529,7 +13540,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A540" s="2">
         <v>41913</v>
       </c>
@@ -13553,7 +13564,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A541" s="2">
         <v>41944</v>
       </c>
@@ -13577,7 +13588,7 @@
         <v>243000</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A542" s="2">
         <v>41974</v>
       </c>
@@ -13601,7 +13612,7 @@
         <v>353000</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A543" s="2">
         <v>42005</v>
       </c>
@@ -13625,7 +13636,7 @@
         <v>329000</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A544" s="2">
         <v>42036</v>
       </c>
@@ -13649,7 +13660,7 @@
         <v>239000</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A545" s="2">
         <v>42064</v>
       </c>
@@ -13673,7 +13684,7 @@
         <v>264000</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A546" s="2">
         <v>42095</v>
       </c>
@@ -13697,7 +13708,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A547" s="2">
         <v>42125</v>
       </c>
@@ -13721,7 +13732,7 @@
         <v>221000</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A548" s="2">
         <v>42156</v>
       </c>
@@ -13745,7 +13756,7 @@
         <v>254000</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A549" s="2">
         <v>42186</v>
       </c>
@@ -13769,7 +13780,7 @@
         <v>231000</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A550" s="2">
         <v>42217</v>
       </c>
@@ -13793,7 +13804,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551" s="2">
         <v>42248</v>
       </c>
@@ -13817,7 +13828,7 @@
         <v>136000</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552" s="2">
         <v>42278</v>
       </c>
@@ -13841,7 +13852,7 @@
         <v>137000</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553" s="2">
         <v>42309</v>
       </c>
@@ -13865,7 +13876,7 @@
         <v>298000</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554" s="2">
         <v>42339</v>
       </c>
@@ -13889,7 +13900,7 @@
         <v>252000</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" s="2">
         <v>42370</v>
       </c>
@@ -13913,7 +13924,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" s="2">
         <v>42401</v>
       </c>
@@ -13937,7 +13948,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" s="2">
         <v>42430</v>
       </c>
@@ -13961,7 +13972,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" s="2">
         <v>42461</v>
       </c>
@@ -13985,7 +13996,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" s="2">
         <v>42491</v>
       </c>
@@ -14009,7 +14020,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" s="2">
         <v>42522</v>
       </c>
@@ -14033,7 +14044,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" s="2">
         <v>42552</v>
       </c>
@@ -14057,7 +14068,7 @@
         <v>292000</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" s="2">
         <v>42583</v>
       </c>
@@ -14081,7 +14092,7 @@
         <v>275000</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" s="2">
         <v>42614</v>
       </c>
@@ -14105,7 +14116,7 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" s="2">
         <v>42644</v>
       </c>
@@ -14129,7 +14140,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" s="2">
         <v>42675</v>
       </c>
@@ -14153,7 +14164,7 @@
         <v>142000</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" s="2">
         <v>42705</v>
       </c>
@@ -14177,7 +14188,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" s="2">
         <v>42736</v>
       </c>
@@ -14201,7 +14212,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" s="2">
         <v>42767</v>
       </c>
@@ -14225,7 +14236,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" s="2">
         <v>42795</v>
       </c>
@@ -14249,7 +14260,7 @@
         <v>219000</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" s="2">
         <v>42826</v>
       </c>
@@ -14273,7 +14284,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" s="2">
         <v>42856</v>
       </c>
@@ -14297,7 +14308,7 @@
         <v>174000</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" s="2">
         <v>42887</v>
       </c>
@@ -14321,7 +14332,7 @@
         <v>152000</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" s="2">
         <v>42917</v>
       </c>
@@ -14345,7 +14356,7 @@
         <v>231000</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" s="2">
         <v>42948</v>
       </c>
@@ -14369,7 +14380,7 @@
         <v>189000</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" s="2">
         <v>42979</v>
       </c>
@@ -14393,7 +14404,7 @@
         <v>169000</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" s="2">
         <v>43009</v>
       </c>
@@ -14417,7 +14428,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" s="2">
         <v>43040</v>
       </c>
@@ -14441,7 +14452,7 @@
         <v>244000</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578" s="2">
         <v>43070</v>
       </c>
@@ -14465,7 +14476,7 @@
         <v>252000</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579" s="2">
         <v>43101</v>
       </c>
@@ -14504,7 +14515,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580" s="2">
         <v>43132</v>
       </c>
@@ -14528,7 +14539,7 @@
         <v>239000</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581" s="2">
         <v>43160</v>
       </c>
@@ -14552,7 +14563,7 @@
         <v>326000</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582" s="2">
         <v>43191</v>
       </c>
@@ -14576,7 +14587,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583" s="2">
         <v>43221</v>
       </c>
@@ -14600,7 +14611,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584" s="2">
         <v>43252</v>
       </c>
@@ -14624,7 +14635,7 @@
         <v>244000</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585" s="2">
         <v>43282</v>
       </c>
@@ -14648,7 +14659,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586" s="2">
         <v>43313</v>
       </c>
@@ -14672,7 +14683,7 @@
         <v>147000</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587" s="2">
         <v>43344</v>
       </c>
@@ -14696,7 +14707,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588" s="2">
         <v>43374</v>
       </c>
@@ -14720,7 +14731,7 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589" s="2">
         <v>43405</v>
       </c>
@@ -14744,7 +14755,7 @@
         <v>237000</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590" s="2">
         <v>43435</v>
       </c>
@@ -14768,7 +14779,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591" s="2">
         <v>43466</v>
       </c>
@@ -14792,7 +14803,7 @@
         <v>222000</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592" s="2">
         <v>43497</v>
       </c>
@@ -14816,7 +14827,7 @@
         <v>311000</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593" s="2">
         <v>43525</v>
       </c>
@@ -14840,7 +14851,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594" s="2">
         <v>43556</v>
       </c>
@@ -14864,7 +14875,7 @@
         <v>189000</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A595" s="2">
         <v>43586</v>
       </c>
@@ -14888,7 +14899,7 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A596" s="2">
         <v>43617</v>
       </c>
@@ -14912,7 +14923,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A597" s="2">
         <v>43647</v>
       </c>
@@ -14936,7 +14947,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A598" s="2">
         <v>43678</v>
       </c>
@@ -14960,7 +14971,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A599" s="2">
         <v>43709</v>
       </c>
@@ -14984,7 +14995,7 @@
         <v>168000</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A600" s="2">
         <v>43739</v>
       </c>
@@ -15008,7 +15019,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A601" s="2">
         <v>43770</v>
       </c>
@@ -15032,7 +15043,7 @@
         <v>156000</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A602" s="2">
         <v>43800</v>
       </c>
@@ -15056,7 +15067,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A603" s="2">
         <v>43831</v>
       </c>
@@ -15080,7 +15091,7 @@
         <v>147000</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A604" s="2">
         <v>43862</v>
       </c>
@@ -15104,7 +15115,7 @@
         <v>273000</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A605" s="2">
         <v>43891</v>
       </c>
@@ -15128,7 +15139,7 @@
         <v>275000</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A606" s="2">
         <v>43922</v>
       </c>
@@ -15152,7 +15163,7 @@
         <v>-870000</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A607" s="2">
         <v>43952</v>
       </c>
@@ -15176,7 +15187,7 @@
         <v>-20687000</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A608" s="2">
         <v>43983</v>
       </c>
@@ -15200,7 +15211,7 @@
         <v>2699000</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A609" s="2">
         <v>44013</v>
       </c>
@@ -15224,7 +15235,7 @@
         <v>4791000</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A610" s="2">
         <v>44044</v>
       </c>
@@ -15248,7 +15259,7 @@
         <v>1734000</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A611" s="2">
         <v>44075</v>
       </c>
@@ -15272,7 +15283,7 @@
         <v>1489000</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A612" s="2">
         <v>44105</v>
       </c>
@@ -15296,7 +15307,7 @@
         <v>672000</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A613" s="2">
         <v>44136</v>
       </c>
@@ -15320,7 +15331,7 @@
         <v>610000</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A614" s="2">
         <v>44166</v>
       </c>
@@ -15344,7 +15355,7 @@
         <v>336000</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A615" s="2">
         <v>44197</v>
       </c>
@@ -15368,7 +15379,7 @@
         <v>-227000</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A616" s="2">
         <v>44228</v>
       </c>
@@ -15392,7 +15403,7 @@
         <v>166000</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A617" s="2">
         <v>44256</v>
       </c>
@@ -15416,7 +15427,7 @@
         <v>468000</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A618" s="2">
         <v>44287</v>
       </c>
@@ -15440,7 +15451,7 @@
         <v>770000</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A619" s="2">
         <v>44317</v>
       </c>
@@ -15464,7 +15475,7 @@
         <v>278000</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A620" s="2">
         <v>44348</v>
       </c>
@@ -15488,7 +15499,7 @@
         <v>583000</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A621" s="2">
         <v>44378</v>
       </c>
@@ -15512,7 +15523,7 @@
         <v>938000</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A622" s="2">
         <v>44409</v>
       </c>
@@ -15536,7 +15547,7 @@
         <v>1053000</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A623" s="2">
         <v>44440</v>
       </c>
@@ -15560,7 +15571,7 @@
         <v>366000</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A624" s="2">
         <v>44470</v>
       </c>
@@ -15584,7 +15595,7 @@
         <v>312000</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A625" s="2">
         <v>44501</v>
       </c>
@@ -15608,7 +15619,7 @@
         <v>546000</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A626" s="2">
         <v>44531</v>
       </c>
@@ -15632,7 +15643,7 @@
         <v>249000</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A627" s="2">
         <v>44562</v>
       </c>
@@ -15656,7 +15667,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A628" s="2">
         <v>44593</v>
       </c>
@@ -15680,7 +15691,7 @@
         <v>481000</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A629" s="2">
         <v>44621</v>
       </c>
@@ -15704,7 +15715,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A630" s="2">
         <v>44652</v>
       </c>
@@ -15728,7 +15739,7 @@
         <v>428000</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A631" s="2">
         <v>44682</v>
       </c>
@@ -15752,7 +15763,7 @@
         <v>436000</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A632" s="2">
         <v>44713</v>
       </c>
@@ -15776,7 +15787,7 @@
         <v>384000</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A633" s="2">
         <v>44743</v>
       </c>
@@ -15800,7 +15811,7 @@
         <v>398000</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A634" s="2">
         <v>44774</v>
       </c>
@@ -15824,7 +15835,7 @@
         <v>526000</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A635" s="2">
         <v>44805</v>
       </c>
@@ -15848,7 +15859,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A636" s="2">
         <v>44835</v>
       </c>
@@ -15872,7 +15883,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A637" s="2">
         <v>44866</v>
       </c>
@@ -15896,7 +15907,7 @@
         <v>284000</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A638" s="2">
         <v>44896</v>
       </c>
@@ -15920,7 +15931,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A639" s="2">
         <v>44927</v>
       </c>
@@ -15944,7 +15955,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A640" s="2">
         <v>44958</v>
       </c>
@@ -15968,7 +15979,7 @@
         <v>504000</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A641" s="2">
         <v>44986</v>
       </c>
@@ -15992,7 +16003,7 @@
         <v>326000</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A642" s="2">
         <v>45017</v>
       </c>
@@ -16016,7 +16027,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A643" s="2">
         <v>45047</v>
       </c>
@@ -16055,7 +16066,7 @@
         <v>294000</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A644" s="2">
         <v>45078</v>
       </c>
@@ -16079,7 +16090,7 @@
         <v>306000</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A645" s="2">
         <v>45108</v>
       </c>
@@ -16103,7 +16114,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A646" s="2">
         <v>45139</v>
       </c>
@@ -16127,7 +16138,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A647" s="2">
         <v>45170</v>
       </c>
@@ -16151,7 +16162,7 @@
         <v>227000</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A648" s="2">
         <v>45200</v>
       </c>
@@ -16175,7 +16186,7 @@
         <v>297000</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A649" s="2">
         <v>45231</v>
       </c>
@@ -16199,7 +16210,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A650" s="2">
         <v>45261</v>
       </c>
@@ -16223,7 +16234,7 @@
         <v>173000</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A651" s="2">
         <v>45292</v>
       </c>
@@ -16247,7 +16258,7 @@
         <v>333000</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A652" s="2">
         <v>45323</v>
       </c>
@@ -16271,7 +16282,7 @@
         <v>229000</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A653" s="2">
         <v>45352</v>
       </c>
@@ -16295,7 +16306,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A654" s="2">
         <v>45383</v>
       </c>
@@ -16319,7 +16330,7 @@
         <v>315000</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A655" s="2">
         <v>45413</v>
       </c>
@@ -16343,7 +16354,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A656" s="2">
         <v>45444</v>
       </c>
@@ -16367,7 +16378,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A657" s="2">
         <v>45474</v>
       </c>
@@ -16391,7 +16402,7 @@
         <v>179000</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A658" s="2">
         <v>45505</v>
       </c>
@@ -16415,7 +16426,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A659" s="2">
         <v>45536</v>
       </c>
@@ -16439,7 +16450,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A660" s="2">
         <v>45566</v>
       </c>
@@ -16463,7 +16474,7 @@
         <v>223000</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A661" s="2">
         <v>45597</v>
       </c>
@@ -16487,7 +16498,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A662" s="2">
         <v>45627</v>
       </c>
@@ -16511,7 +16522,7 @@
         <v>212000</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A663" s="2">
         <v>45658</v>
       </c>
@@ -16535,7 +16546,7 @@
         <v>307000</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A664" s="2">
         <v>45689</v>
       </c>
@@ -16559,7 +16570,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A665" s="2">
         <v>45717</v>
       </c>
@@ -16583,7 +16594,7 @@
         <v>117000</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A666" s="2">
         <v>45748</v>
       </c>
@@ -16607,7 +16618,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A667" s="2">
         <v>45778</v>
       </c>
@@ -16631,7 +16642,7 @@
         <v>147000</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A668" s="2">
         <v>45809</v>
       </c>
@@ -16655,7 +16666,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A669" s="2">
         <v>45839</v>
       </c>
@@ -16679,7 +16690,7 @@
         <v>-13000</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A670" s="2">
         <v>45870</v>
       </c>
@@ -16703,7 +16714,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A671" s="2">
         <v>45901</v>
       </c>
@@ -16721,13 +16732,13 @@
         <v>119000</v>
       </c>
       <c r="F671" s="3">
-        <v>53</v>
+        <v>53000</v>
       </c>
       <c r="G671" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A672" s="2">
         <v>45931</v>
       </c>
@@ -16748,7 +16759,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A673" s="2">
         <v>45962</v>
       </c>
@@ -16772,7 +16783,7 @@
         <v>-105000</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A674" s="2">
         <v>45992</v>
       </c>

--- a/data/macro/USA/Nonfarm Payrolls.xlsx
+++ b/data/macro/USA/Nonfarm Payrolls.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D3E7EC-6135-4110-88E4-829726BB819A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E91C19A-A98C-4475-A283-AB2654D217DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAYEMS" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -80,7 +81,7 @@
     <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="180" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,19 +116,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -152,7 +140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -177,8 +165,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -195,6 +182,4897 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PAYEMS!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>PAYEMS!$B$2:$B$676</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="675"/>
+                <c:pt idx="0">
+                  <c:v>25570</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25605</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25633</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25661</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25689</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25724</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25752</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25787</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25815</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25843</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25878</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25906</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25934</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25969</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26025</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26060</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26088</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26116</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26151</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>26179</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26207</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26242</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26270</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26305</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26333</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26361</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26396</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26424</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26452</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26487</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26515</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26543</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26578</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26606</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26634</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26669</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26697</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26725</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26760</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26788</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>26816</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>26851</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>26879</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>26914</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>26942</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26970</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>27005</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>27033</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>27061</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>27089</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27124</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>27152</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>27187</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>27215</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>27243</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>27278</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>27306</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>27334</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>27369</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>27397</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>27432</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>27460</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>27488</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>27516</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>27551</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>27579</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>27607</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>27642</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>27670</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>27705</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>27733</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27761</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>27796</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>27824</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>27852</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>27887</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>27915</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>27943</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>27978</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>28006</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>28034</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>28069</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>28097</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>28132</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>28160</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>28188</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>28216</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>28251</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>28279</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>28307</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>28342</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>28370</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>28405</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>28433</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>28461</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>28496</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>28524</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>28552</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>28587</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>28615</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>28643</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>28678</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>28706</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>28734</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28769</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>28797</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>28825</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>28860</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>28888</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28916</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>28951</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>28979</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>29007</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>29042</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>29070</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>29105</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>29133</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>29161</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>29196</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>29224</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>29252</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>29287</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>29315</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>29343</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>29378</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>29406</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>29434</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>29469</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>29497</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>29532</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>29560</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>29588</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>29623</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>29651</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>29679</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>29707</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>29742</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>29770</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>29805</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>29833</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>29861</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>29896</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>29924</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>29952</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>29987</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>30015</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>30043</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>30078</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>30106</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>30134</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>30169</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>30197</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>30225</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>30260</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>30288</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>30323</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>30351</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>30379</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>30407</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>30442</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>30470</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>30498</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>30533</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>30561</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>30596</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>30624</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>30652</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>30687</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>30715</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>30743</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>30778</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>30806</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>30834</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>30869</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>30897</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>30932</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>30960</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>30988</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>31023</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>31051</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>31079</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>31107</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>31142</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>31170</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>31205</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>31233</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>31261</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>31296</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>31324</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>31352</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>31387</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>31415</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>31450</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>31478</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>31506</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>31534</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>31569</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>31597</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>31625</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>31660</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>31688</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>31723</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>31751</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>31779</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>31814</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>31842</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>31870</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>31898</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>31933</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>31961</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>31996</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>32024</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>32052</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>32087</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>32115</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>32143</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>32178</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>32206</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>32234</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>32269</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>32297</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>32325</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>32360</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>32388</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>32423</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>32451</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>32479</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>32514</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>32542</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>32570</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>32605</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>32633</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>32661</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>32696</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>32724</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>32752</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>32787</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>32815</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>32843</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>32878</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>32906</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>32934</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>32969</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>32997</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>33025</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>33060</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>33088</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>33123</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>33151</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>33179</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>33214</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>33242</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>33270</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>33298</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>33333</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>33361</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>33396</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>33424</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>33452</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>33487</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>33515</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>33543</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>33578</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>33606</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>33641</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>33669</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>33697</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>33725</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>33760</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>33788</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>33823</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>33851</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>33879</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>33914</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>33942</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>33970</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>34005</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>34033</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>34061</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>34096</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>34124</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>34152</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>34187</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>34215</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>34243</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>34278</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>34306</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>34341</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>34369</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>34397</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>34425</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>34460</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>34488</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>34516</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>34551</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>34579</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>34614</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>34642</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>34670</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>34705</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>34733</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>34761</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>34796</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>34824</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>34852</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>34887</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>34915</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>34943</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>34978</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>35006</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>35034</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>35069</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>35097</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>35125</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>35160</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>35188</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>35223</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>35251</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>35279</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>35314</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>35342</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>35370</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>35405</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>35433</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>35468</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>35496</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>35524</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>35552</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>35587</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>35615</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>35643</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>35678</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>35706</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>35741</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>35769</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>35797</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>35832</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>35860</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>35888</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>35916</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>35951</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>35979</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>36014</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>36042</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>36070</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>36105</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>36133</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>36161</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>36196</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>36224</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>36252</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>36287</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>36315</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>36343</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>36378</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>36406</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>36434</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>36469</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>36497</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>36532</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>36560</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>36588</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>36623</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>36651</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>36679</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>36714</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>36742</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>36770</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>36805</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>36833</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>36868</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>36896</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>36924</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>36959</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>36987</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>37015</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>37043</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>37078</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>37106</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>37141</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>37169</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>37197</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>37232</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>37260</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>37288</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>37323</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>37351</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>37379</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>37414</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>37442</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>37470</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>37505</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>37533</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>37561</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>37596</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>37631</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>37659</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>37687</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>37715</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>37743</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>37778</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>37805</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>37834</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>37869</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>37897</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>37932</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>37960</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>37995</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>38023</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>38051</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>38079</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>38114</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>38142</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>38170</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>38205</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>38233</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>38268</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>38296</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>38324</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>38359</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>38387</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>38415</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>38443</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>38478</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>38506</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>38541</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>38569</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>38597</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>38632</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>38660</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>38688</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>38723</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>38751</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>38786</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>38814</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>38842</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>38870</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>38905</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>38933</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>38961</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>38996</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>39024</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>39059</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>39087</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>39115</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>39150</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>39178</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>39206</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>39234</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>39269</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>39297</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>39332</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>39360</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>39388</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>39423</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>39451</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>39479</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>39514</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>39542</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>39570</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>39605</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>39632</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>39661</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>39696</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>39724</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>39759</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>39787</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>39822</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>39850</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>39878</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>39906</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>39941</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>39969</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>39996</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>40032</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>40060</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>40088</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>40123</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>40151</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>40186</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>40214</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>40242</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>40270</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>40305</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>40333</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>40361</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>40396</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>40424</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>40459</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>40487</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>40515</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>40550</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>40578</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>40606</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>40634</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>40669</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>40697</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>40732</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>40760</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>40788</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>40823</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>40851</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>40879</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>40914</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>40942</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>40977</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>41005</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>41033</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>41061</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>41096</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>41124</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>41159</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>41187</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>41215</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>41250</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>41278</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>41306</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>41341</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>41369</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>41397</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>41432</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>41460</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>41488</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>41523</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>41569</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>41586</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>41614</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>41649</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>41677</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>41705</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>41733</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>41761</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>41796</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>41823</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>41852</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>41887</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>41915</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>41950</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>41978</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>42013</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>42041</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>42069</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>42097</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>42132</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>42160</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>42187</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>42223</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>42251</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>42279</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>42314</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>42342</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>42377</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>42405</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>42433</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>42461</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>42496</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>42524</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>42559</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>42587</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>42615</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>42650</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>42678</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>42706</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>42741</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>42769</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>42804</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>42832</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>42860</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>42888</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>42923</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>42951</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>42979</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>43014</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>43042</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>43077</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>43105</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>43133</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>43168</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>43196</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>43224</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>43252</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>43287</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>43315</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>43350</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>43378</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>43406</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>43441</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>43469</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>43497</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>43532</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>43560</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>43588</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>43623</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>43651</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>43679</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>43714</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>43742</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>43770</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>43805</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>43840</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>43868</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>43896</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>43924</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>43959</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>43987</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>44014</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>44050</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>44078</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>44106</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>44141</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>44169</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>44204</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>44232</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>44260</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>44288</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>44323</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>44351</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>44379</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>44414</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>44442</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>44477</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>44505</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>44533</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>44568</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>44596</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>44624</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>44652</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>44687</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>44715</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>44750</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>44778</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>44806</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>44841</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>44869</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>44897</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>44932</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>44960</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>44995</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>45023</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>45051</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>45079</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>45114</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>45142</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>45170</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>45205</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>45233</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>45268</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>45296</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>45324</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>45359</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>45387</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>45415</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>45450</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>45478</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>45506</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>45541</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>45632</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>45667</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>45695</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>45723</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>45779</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>45814</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>45841</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>45905</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>45981</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>46031</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>46087</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PAYEMS!$E$2:$E$676</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="675"/>
+                <c:pt idx="0">
+                  <c:v>153000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-64000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-104000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-225000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-94000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-120000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-429000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-110000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>381000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>76000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-60000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>53000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>178000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>62000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>55000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>247000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>204000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>262000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>337000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>207000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>293000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>304000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>293000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-52000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>410000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>294000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>303000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>351000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>396000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>268000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>170000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>191000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>241000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>255000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>306000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>123000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>69000</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>86000</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>165000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-16000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-8000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-368000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-604000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-360000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-378000</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-270000</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-188000</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>162000</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-103000</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>249000</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>386000</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>305000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>145000</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>338000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>488000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>311000</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>232000</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>243000</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>65000</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>188000</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>332000</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>211000</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>244000</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>296000</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>403000</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>338000</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>360000</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>399000</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>348000</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>238000</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>458000</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>262000</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>379000</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>235000</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>187000</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>353000</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>513000</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>702000</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>346000</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>442000</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>254000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>276000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>137000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>336000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>437000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>282000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>137000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>244000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>426000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>-62000</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>373000</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>318000</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>106000</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>82000</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>94000</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>97000</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>129000</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>-144000</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>-431000</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>-320000</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>-262000</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>260000</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>113000</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>281000</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>257000</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>195000</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>94000</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>105000</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>73000</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>197000</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>-36000</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>-87000</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>-99000</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>-209000</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>-278000</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>-326000</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>-5000</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-130000</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>-280000</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>-45000</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>-243000</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>-342000</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>-158000</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>-181000</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>-277000</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>-123000</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>-14000</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>-75000</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>276000</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>277000</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>379000</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>418000</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>-308000</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1115000</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>271000</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>353000</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>356000</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>446000</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>481000</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>275000</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>363000</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>308000</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>379000</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>313000</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>242000</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>310000</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>286000</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>349000</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>266000</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>346000</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>196000</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>274000</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>146000</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>190000</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>193000</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>203000</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>188000</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>209000</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>167000</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>107000</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>94000</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>187000</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>127000</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>-94000</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>318000</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>347000</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>186000</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>186000</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>205000</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>232000</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>249000</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>338000</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>226000</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>347000</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>228000</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>492000</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>232000</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>294000</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>94000</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>453000</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>276000</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>245000</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>363000</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>339000</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>268000</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>339000</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>290000</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>262000</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>258000</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>193000</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>173000</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>111000</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>277000</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>96000</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>335000</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>248000</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>152000</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>-28000</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>-221000</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>-88000</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>-159000</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>-150000</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>-56000</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>-120000</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>-305000</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>-158000</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>-211000</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>-125000</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>97000</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>-36000</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>-57000</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>53000</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>-63000</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>54000</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>159000</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>127000</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>67000</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>141000</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>180000</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>138000</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>211000</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>310000</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>242000</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>-49000</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>308000</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>267000</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>181000</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>298000</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>239000</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>286000</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>262000</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>312000</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>272000</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>465000</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>349000</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>334000</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>316000</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>378000</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>277000</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>352000</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>213000</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>275000</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>326000</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>203000</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>162000</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>-16000</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>235000</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>102000</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>248000</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>242000</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>154000</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>149000</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>133000</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>-19000</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>431000</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>267000</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>164000</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>321000</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>288000</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>256000</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>298000</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>235000</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>303000</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>316000</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>292000</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>259000</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>267000</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>313000</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>-39000</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>512000</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>341000</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>306000</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>303000</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>276000</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>196000</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>151000</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>279000</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>406000</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>347000</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>198000</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>282000</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>347000</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>411000</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>107000</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>376000</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>211000</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>261000</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>319000</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>166000</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>292000</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>295000</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>467000</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>287000</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>226000</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>-47000</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>179000</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>-15000</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>-15000</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>-27000</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>71000</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>-25000</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>-282000</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>-38000</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>-131000</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>-112000</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>-160000</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>-241000</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>-325000</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>-294000</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>-171000</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>-139000</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>-134000</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>-20000</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>-80000</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>-8000</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>56000</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>-84000</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>-16000</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>-60000</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>-157000</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>91000</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>-151000</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>-210000</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>-44000</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>-10000</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>-43000</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>103000</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>196000</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>123000</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>331000</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>248000</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>308000</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>74000</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>132000</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>162000</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>345000</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>129000</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>134000</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>239000</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>363000</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>176000</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>243000</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>375000</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>196000</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>66000</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>84000</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>337000</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>158000</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>277000</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>315000</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>281000</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>182000</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>77000</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>206000</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>185000</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>209000</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>172000</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>237000</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>97000</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>177000</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>190000</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>69000</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>93000</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>96000</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>170000</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>115000</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>82000</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>-22000</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>-63000</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>-80000</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>-20000</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>-49000</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>-62000</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>-51000</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>-84000</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>-159000</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>-240000</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>-533000</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>-524000</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>-598000</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>-651000</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>-663000</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>-539000</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>-345000</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>-467000</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>-247000</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>-216000</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>-263000</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>-190000</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>-11000</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>-85000</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>-20000</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>-36000</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>162000</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>290000</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>431000</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>-125000</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>-131000</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>-54000</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>-95000</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>151000</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>103000</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>192000</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>244000</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>54000</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>117000</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>103000</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>243000</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>115000</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>69000</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>163000</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>96000</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>146000</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>155000</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>236000</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>88000</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>165000</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>175000</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>195000</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>162000</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>169000</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>204000</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>203000</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>74000</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>113000</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>175000</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>192000</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>288000</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>288000</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>209000</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>248000</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>321000</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>252000</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>257000</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>295000</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>126000</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>280000</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>173000</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>271000</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>211000</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>292000</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>151000</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>242000</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>287000</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>255000</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>151000</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>161000</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>178000</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>235000</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>98000</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>211000</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>138000</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>209000</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>-33000</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>261000</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>228000</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>313000</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>103000</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>164000</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>213000</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>201000</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>134000</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>155000</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>312000</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>304000</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>196000</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>263000</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>164000</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>136000</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>128000</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>266000</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>145000</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>273000</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>-701000</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>-20537000</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>2509000</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>4800000</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>1763000</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>1371000</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>661000</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>638000</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>245000</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>-140000</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>379000</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>916000</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>266000</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>559000</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>850000</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>943000</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>235000</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>194000</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>531000</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>199000</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>467000</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>678000</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>431000</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>428000</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>372000</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>528000</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>315000</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>263000</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>261000</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>263000</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>517000</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>311000</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>236000</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>253000</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>339000</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>209000</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>187000</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>187000</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>336000</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>199000</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>353000</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>275000</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>303000</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>175000</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>272000</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>206000</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>254000</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>256000</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>143000</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>151000</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>228000</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>177000</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>139000</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>147000</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>73000</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>119000</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>-105000</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>64000</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>-92000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AA78-4CE4-9FB3-4A41A095A700}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1318222271"/>
+        <c:axId val="1840585631"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1318222271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="47848"/>
+          <c:min val="25569"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1840585631"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="5"/>
+        <c:majorTimeUnit val="years"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1840585631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="-500000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1318222271"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{458D1C40-924F-46C1-9915-5CA7070BD228}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -460,7 +5338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G675"/>
+  <dimension ref="A1:G676"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="5" bestFit="1" customWidth="1"/>
@@ -16054,7 +20932,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D675" si="10">IF(
+        <f t="shared" ref="D643:D676" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -16823,7 +21701,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="5">
         <v>46023</v>
       </c>
@@ -16845,6 +21723,30 @@
       </c>
       <c r="G675" s="9">
         <v>48000</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A676" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B676" s="5">
+        <v>46087</v>
+      </c>
+      <c r="C676" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D676" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="E676" s="9">
+        <v>-92000</v>
+      </c>
+      <c r="F676" s="9">
+        <v>58000</v>
+      </c>
+      <c r="G676" s="9">
+        <v>126000</v>
       </c>
     </row>
   </sheetData>
@@ -16855,28 +21757,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F6FFE7-935B-4937-A09B-D8028EE7988F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7EC8A6-10AD-4108-A188-3444D7C45400}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="11.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="11.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2" s="11" t="s">
+    <row r="2" spans="2:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
+    <row r="3" spans="2:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/macro/USA/Nonfarm Payrolls.xlsx
+++ b/data/macro/USA/Nonfarm Payrolls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E91C19A-A98C-4475-A283-AB2654D217DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDB80B0-41D1-4CF1-A216-6B3328A8387B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAYEMS" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4439,6 +4448,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4446,7 +4456,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5338,14 +5347,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G676"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G677"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.3984375" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -20932,7 +20941,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D676" si="10">IF(
+        <f t="shared" ref="D643:D677" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -21749,6 +21758,30 @@
         <v>126000</v>
       </c>
     </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B677" s="5">
+        <v>46115</v>
+      </c>
+      <c r="C677" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D677" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E677" s="9">
+        <v>178000</v>
+      </c>
+      <c r="F677" s="9">
+        <v>65000</v>
+      </c>
+      <c r="G677" s="9">
+        <v>-133000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21759,7 +21792,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F6FFE7-935B-4937-A09B-D8028EE7988F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21770,14 +21803,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7EC8A6-10AD-4108-A188-3444D7C45400}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
     <col min="2" max="2" width="11.5" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
@@ -21785,7 +21818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="10" t="s">
         <v>10</v>
       </c>

--- a/data/macro/USA/Nonfarm Payrolls.xlsx
+++ b/data/macro/USA/Nonfarm Payrolls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDB80B0-41D1-4CF1-A216-6B3328A8387B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30038BF1-7A54-45B0-AF45-017FACF4C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5347,7 +5347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G677"/>
+  <dimension ref="A1:G678"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="5" bestFit="1" customWidth="1"/>
@@ -20941,7 +20941,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D677" si="10">IF(
+        <f t="shared" ref="D643:D678" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -21780,6 +21780,27 @@
       </c>
       <c r="G677" s="9">
         <v>-133000</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A678" s="5">
+        <v>46113</v>
+      </c>
+      <c r="B678" s="5">
+        <v>46150</v>
+      </c>
+      <c r="C678" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D678" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="F678" s="9">
+        <v>65000</v>
+      </c>
+      <c r="G678" s="9">
+        <v>178000</v>
       </c>
     </row>
   </sheetData>
